--- a/base_datas/media_nacional_detalhamento.xlsx
+++ b/base_datas/media_nacional_detalhamento.xlsx
@@ -593,70 +593,70 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>785.0161963624008</v>
+        <v>783.9872492523704</v>
       </c>
       <c r="B2">
-        <v>180.9512246234176</v>
+        <v>181.2480122502259</v>
       </c>
       <c r="C2">
-        <v>7535.596714562197</v>
+        <v>7546.31893936303</v>
       </c>
       <c r="D2">
-        <v>459.0692486007583</v>
+        <v>460.1872176527446</v>
       </c>
       <c r="E2">
-        <v>721.4671589670048</v>
+        <v>721.0516422908664</v>
       </c>
       <c r="F2">
-        <v>61.34664108726943</v>
+        <v>61.15680043647811</v>
       </c>
       <c r="G2">
-        <v>18.13456026894213</v>
+        <v>16.06194288165421</v>
       </c>
       <c r="H2">
-        <v>256.6162582674043</v>
+        <v>257.0510199524927</v>
       </c>
       <c r="I2">
-        <v>70.34547167474553</v>
+        <v>70.44295624048699</v>
       </c>
       <c r="J2">
-        <v>2.318740029603504</v>
+        <v>1.92330209400696</v>
       </c>
       <c r="K2">
-        <v>4537.619404882741</v>
+        <v>4546.178447362161</v>
       </c>
       <c r="L2">
-        <v>1938.842607909603</v>
+        <v>1939.083837205192</v>
       </c>
       <c r="M2">
-        <v>1060.270717482691</v>
+        <v>1061.831997619788</v>
       </c>
       <c r="N2">
-        <v>322.5149649947491</v>
+        <v>322.532054289919</v>
       </c>
       <c r="O2">
-        <v>110.8446652461726</v>
+        <v>112.8943506162525</v>
       </c>
       <c r="P2">
-        <v>10.62665377292406</v>
+        <v>10.52980208955671</v>
       </c>
       <c r="Q2">
         <v>10.78904654154204</v>
       </c>
       <c r="R2">
-        <v>73.55191672171813</v>
+        <v>73.67231205743848</v>
       </c>
       <c r="S2">
-        <v>125.7777394042518</v>
+        <v>125.7300852650952</v>
       </c>
       <c r="T2">
-        <v>91.26054366302479</v>
+        <v>91.6224259626364</v>
       </c>
       <c r="U2">
-        <v>280.6616842066475</v>
+        <v>280.2962876016952</v>
       </c>
       <c r="V2">
-        <v>224.379248879704</v>
+        <v>224.2824514745904</v>
       </c>
       <c r="W2">
         <v>4203.961932344067</v>
@@ -665,70 +665,70 @@
         <v>660.8749918098674</v>
       </c>
       <c r="Y2">
-        <v>5.424277189996325</v>
+        <v>5.023263157530238</v>
       </c>
       <c r="Z2">
-        <v>27.87990517766868</v>
+        <v>27.72157170656813</v>
       </c>
       <c r="AA2">
-        <v>40.35091026121903</v>
+        <v>40.28688394947764</v>
       </c>
       <c r="AB2">
-        <v>1.008543988488698E-16</v>
+        <v>1.795603163639464E-16</v>
       </c>
       <c r="AC2">
-        <v>12.73007207110482</v>
+        <v>10.33942533847607</v>
       </c>
       <c r="AD2">
-        <v>10.39237772493542</v>
+        <v>10.20821546934906</v>
       </c>
       <c r="AE2">
-        <v>33.8248801955621</v>
+        <v>34.10551275155728</v>
       </c>
       <c r="AF2">
-        <v>9.806215829025755</v>
+        <v>6.755458275271039</v>
       </c>
       <c r="AG2">
-        <v>3022.811993947558</v>
+        <v>3028.015140987054</v>
       </c>
       <c r="AH2">
         <v>467.5037520550409</v>
       </c>
       <c r="AI2">
-        <v>198.2630925975667</v>
+        <v>198.7865570901909</v>
       </c>
       <c r="AJ2">
-        <v>670.4519011151408</v>
+        <v>671.5028308930442</v>
       </c>
       <c r="AK2">
-        <v>120.0970056452453</v>
+        <v>120.2833000939857</v>
       </c>
       <c r="AL2">
-        <v>390.6600442146365</v>
+        <v>390.9511283383356</v>
       </c>
       <c r="AM2">
-        <v>40.53887823915556</v>
+        <v>40.7125092065367</v>
       </c>
       <c r="AN2">
-        <v>141.0548202417746</v>
+        <v>141.8375425478177</v>
       </c>
       <c r="AO2">
-        <v>1484.931588553425</v>
+        <v>1485.133875396584</v>
       </c>
       <c r="AP2">
-        <v>155.4892148845773</v>
+        <v>155.3239736314658</v>
       </c>
       <c r="AQ2">
-        <v>129.6698493162134</v>
+        <v>129.6175218534575</v>
       </c>
       <c r="AR2">
-        <v>20.24652714581114</v>
+        <v>20.25760572948272</v>
       </c>
       <c r="AS2">
-        <v>43.97749600459942</v>
+        <v>43.85350179542319</v>
       </c>
       <c r="AT2">
-        <v>165.8125893357729</v>
+        <v>166.2740059602171</v>
       </c>
       <c r="AU2">
         <v>1</v>

--- a/base_datas/media_nacional_detalhamento.xlsx
+++ b/base_datas/media_nacional_detalhamento.xlsx
@@ -593,70 +593,70 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>785.0161963624008</v>
+        <v>783.8709472269916</v>
       </c>
       <c r="B2">
-        <v>180.9512246234176</v>
+        <v>181.2209619704638</v>
       </c>
       <c r="C2">
-        <v>7535.596714562197</v>
+        <v>7545.231789483922</v>
       </c>
       <c r="D2">
-        <v>459.0692486007583</v>
+        <v>460.1490251557524</v>
       </c>
       <c r="E2">
-        <v>721.4671589670048</v>
+        <v>720.9450434299076</v>
       </c>
       <c r="F2">
-        <v>61.34664108726943</v>
+        <v>61.14685437715292</v>
       </c>
       <c r="G2">
-        <v>18.13456026894213</v>
+        <v>16.04876845742728</v>
       </c>
       <c r="H2">
-        <v>256.6162582674043</v>
+        <v>256.951765751568</v>
       </c>
       <c r="I2">
-        <v>70.34547167474553</v>
+        <v>70.42903186572927</v>
       </c>
       <c r="J2">
-        <v>2.318740029603504</v>
+        <v>1.92330209400696</v>
       </c>
       <c r="K2">
-        <v>4537.619404882741</v>
+        <v>4545.5180794935</v>
       </c>
       <c r="L2">
-        <v>1938.842607909603</v>
+        <v>1938.818496491412</v>
       </c>
       <c r="M2">
-        <v>1060.270717482691</v>
+        <v>1061.670296760012</v>
       </c>
       <c r="N2">
-        <v>322.5149649947491</v>
+        <v>322.5181583038332</v>
       </c>
       <c r="O2">
-        <v>110.8446652461726</v>
+        <v>112.858056328481</v>
       </c>
       <c r="P2">
-        <v>10.62665377292406</v>
+        <v>10.52980208955671</v>
       </c>
       <c r="Q2">
         <v>10.78904654154204</v>
       </c>
       <c r="R2">
-        <v>73.55191672171813</v>
+        <v>73.65952136962071</v>
       </c>
       <c r="S2">
-        <v>125.7777394042518</v>
+        <v>125.7085156104253</v>
       </c>
       <c r="T2">
-        <v>91.26054366302479</v>
+        <v>91.60814022257104</v>
       </c>
       <c r="U2">
-        <v>280.6616842066475</v>
+        <v>280.254449688958</v>
       </c>
       <c r="V2">
-        <v>224.379248879704</v>
+        <v>224.2525277342187</v>
       </c>
       <c r="W2">
         <v>4203.961932344067</v>
@@ -665,70 +665,70 @@
         <v>660.8749918098674</v>
       </c>
       <c r="Y2">
-        <v>5.424277189996325</v>
+        <v>5.021973487913414</v>
       </c>
       <c r="Z2">
-        <v>27.87990517766868</v>
+        <v>27.71730009776945</v>
       </c>
       <c r="AA2">
-        <v>40.35091026121903</v>
+        <v>40.27859669138937</v>
       </c>
       <c r="AB2">
-        <v>1.008543988488698E-16</v>
+        <v>1.795603163639464E-16</v>
       </c>
       <c r="AC2">
-        <v>12.73007207110482</v>
+        <v>10.32462120025367</v>
       </c>
       <c r="AD2">
-        <v>10.39237772493542</v>
+        <v>10.20821546934906</v>
       </c>
       <c r="AE2">
-        <v>33.8248801955621</v>
+        <v>34.10551275155728</v>
       </c>
       <c r="AF2">
-        <v>9.806215829025755</v>
+        <v>6.755458275271039</v>
       </c>
       <c r="AG2">
-        <v>3022.811993947558</v>
+        <v>3027.579975909575</v>
       </c>
       <c r="AH2">
         <v>467.5037520550409</v>
       </c>
       <c r="AI2">
-        <v>198.2630925975667</v>
+        <v>198.7591671446032</v>
       </c>
       <c r="AJ2">
-        <v>670.4519011151408</v>
+        <v>671.4004229827376</v>
       </c>
       <c r="AK2">
-        <v>120.0970056452453</v>
+        <v>120.2631734610833</v>
       </c>
       <c r="AL2">
-        <v>390.6600442146365</v>
+        <v>390.9511283383356</v>
       </c>
       <c r="AM2">
-        <v>40.53887823915556</v>
+        <v>40.70613966707398</v>
       </c>
       <c r="AN2">
-        <v>141.0548202417746</v>
+        <v>141.8311605927099</v>
       </c>
       <c r="AO2">
-        <v>1484.931588553425</v>
+        <v>1484.933706514375</v>
       </c>
       <c r="AP2">
-        <v>155.4892148845773</v>
+        <v>155.3032683010084</v>
       </c>
       <c r="AQ2">
-        <v>129.6698493162134</v>
+        <v>129.5967766690234</v>
       </c>
       <c r="AR2">
-        <v>20.24652714581114</v>
+        <v>20.25760572948272</v>
       </c>
       <c r="AS2">
-        <v>43.97749600459942</v>
+        <v>43.85350179542319</v>
       </c>
       <c r="AT2">
-        <v>165.8125893357729</v>
+        <v>166.2466723130861</v>
       </c>
       <c r="AU2">
         <v>1</v>
